--- a/AST.xlsx
+++ b/AST.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580C3BB7-E68A-0D40-9D15-59CCEFA6F158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067D480F-C7A3-4C4C-AA8A-DCF2EC275E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AST" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
   <si>
     <t>Astar Boyu</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>12.5cm</t>
+  </si>
+  <si>
+    <t>DENEME</t>
   </si>
 </sst>
 </file>
@@ -520,8 +523,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Çıkış" xfId="1" builtinId="21"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Output" xfId="1" builtinId="21"/>
   </cellStyles>
   <dxfs count="19">
     <dxf>
@@ -1180,7 +1183,7 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Kalınlık" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Astar Boyu" dataDxfId="10"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Taban Boyu" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{84EADB6C-7CDD-F14C-A21A-55140F017ABC}" name="Ağız Boyu" dataDxfId="8" dataCellStyle="Output"/>
+    <tableColumn id="14" xr3:uid="{84EADB6C-7CDD-F14C-A21A-55140F017ABC}" name="Ağız Boyu" dataDxfId="8"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Astar Ağırlık" dataDxfId="7"/>
     <tableColumn id="8" xr3:uid="{A009F055-9F4E-4939-80FA-CF766AEF6E7A}" name="Kulp Tip" dataDxfId="6"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Kulp Ağırlık" dataDxfId="5"/>
@@ -1485,24 +1488,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="133" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="132.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -1516,7 +1519,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -1560,7 +1563,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>44</v>
       </c>
@@ -1596,7 +1599,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>45</v>
       </c>
@@ -1632,7 +1635,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>46</v>
       </c>
@@ -1670,7 +1673,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>47</v>
       </c>
@@ -1708,7 +1711,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>48</v>
       </c>
@@ -1744,7 +1747,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>39</v>
       </c>
@@ -1760,7 +1763,9 @@
       <c r="E8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="7"/>
+      <c r="F8" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -1776,7 +1781,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>40</v>
       </c>
@@ -1810,7 +1815,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>41</v>
       </c>
@@ -1846,7 +1851,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>42</v>
       </c>
@@ -1882,7 +1887,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>43</v>
       </c>
@@ -1916,7 +1921,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -1932,7 +1937,7 @@
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
     </row>
-    <row r="14" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -1948,7 +1953,7 @@
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
     </row>
-    <row r="15" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -1964,7 +1969,7 @@
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
     </row>
-    <row r="16" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -1980,7 +1985,7 @@
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
     </row>
-    <row r="17" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>

--- a/AST.xlsx
+++ b/AST.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067D480F-C7A3-4C4C-AA8A-DCF2EC275E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAB3A83-5FF1-479E-AD7C-B89D806EB143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="59">
   <si>
     <t>Astar Boyu</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>DENEME</t>
+  </si>
+  <si>
+    <t>DENEME2</t>
   </si>
 </sst>
 </file>
@@ -1797,7 +1800,9 @@
       <c r="E9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="7"/>
+      <c r="F9" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="G9" s="7" t="s">
         <v>28</v>
       </c>

--- a/AST.xlsx
+++ b/AST.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAB3A83-5FF1-479E-AD7C-B89D806EB143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1369F6-7B71-4B87-B727-4B5DE6D0CC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="60">
   <si>
     <t>Astar Boyu</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>DENEME2</t>
+  </si>
+  <si>
+    <t>DENEME3</t>
   </si>
 </sst>
 </file>
@@ -1836,7 +1839,9 @@
       <c r="E10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="7"/>
+      <c r="F10" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="G10" s="7" t="s">
         <v>29</v>
       </c>

--- a/AST.xlsx
+++ b/AST.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1369F6-7B71-4B87-B727-4B5DE6D0CC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D11E3D-BF9E-4DB5-857F-647470880B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="57">
   <si>
     <t>Astar Boyu</t>
   </si>
@@ -228,15 +228,6 @@
   </si>
   <si>
     <t>12.5cm</t>
-  </si>
-  <si>
-    <t>DENEME</t>
-  </si>
-  <si>
-    <t>DENEME2</t>
-  </si>
-  <si>
-    <t>DENEME3</t>
   </si>
 </sst>
 </file>
@@ -1769,9 +1760,7 @@
       <c r="E8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>57</v>
-      </c>
+      <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -1803,9 +1792,7 @@
       <c r="E9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="F9" s="7"/>
       <c r="G9" s="7" t="s">
         <v>28</v>
       </c>
@@ -1839,9 +1826,7 @@
       <c r="E10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="F10" s="7"/>
       <c r="G10" s="7" t="s">
         <v>29</v>
       </c>

--- a/AST.xlsx
+++ b/AST.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D11E3D-BF9E-4DB5-857F-647470880B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52962FBF-BEA3-484B-BC5A-5A553AF0D531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
   <si>
     <t>Astar Boyu</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>12.5cm</t>
+  </si>
+  <si>
+    <t>DENEME1</t>
   </si>
 </sst>
 </file>
@@ -1724,7 +1727,9 @@
       <c r="E7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="9"/>
+      <c r="F7" s="9" t="s">
+        <v>57</v>
+      </c>
       <c r="G7" s="9" t="s">
         <v>31</v>
       </c>

--- a/AST.xlsx
+++ b/AST.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52962FBF-BEA3-484B-BC5A-5A553AF0D531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3503776-6BEB-4EB6-BE50-5104FBECD388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="57">
   <si>
     <t>Astar Boyu</t>
   </si>
@@ -228,9 +228,6 @@
   </si>
   <si>
     <t>12.5cm</t>
-  </si>
-  <si>
-    <t>DENEME1</t>
   </si>
 </sst>
 </file>
@@ -1727,9 +1724,7 @@
       <c r="E7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>57</v>
-      </c>
+      <c r="F7" s="9"/>
       <c r="G7" s="9" t="s">
         <v>31</v>
       </c>

--- a/AST.xlsx
+++ b/AST.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3503776-6BEB-4EB6-BE50-5104FBECD388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F32151A-BFF5-44AE-8935-1CA2798EF6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
   <si>
     <t>Astar Boyu</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>12.5cm</t>
+  </si>
+  <si>
+    <t>DENEME</t>
   </si>
 </sst>
 </file>
@@ -1724,7 +1727,9 @@
       <c r="E7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="9"/>
+      <c r="F7" s="9" t="s">
+        <v>57</v>
+      </c>
       <c r="G7" s="9" t="s">
         <v>31</v>
       </c>

--- a/AST.xlsx
+++ b/AST.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F32151A-BFF5-44AE-8935-1CA2798EF6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84452E4B-A62E-4800-8842-810E9D631AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="57">
   <si>
     <t>Astar Boyu</t>
   </si>
@@ -228,9 +228,6 @@
   </si>
   <si>
     <t>12.5cm</t>
-  </si>
-  <si>
-    <t>DENEME</t>
   </si>
 </sst>
 </file>
@@ -1727,9 +1724,7 @@
       <c r="E7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>57</v>
-      </c>
+      <c r="F7" s="9"/>
       <c r="G7" s="9" t="s">
         <v>31</v>
       </c>
